--- a/output/results_0221_KB_review.xlsx
+++ b/output/results_0221_KB_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dulin/Dropbox/UTHealth/SAFElab/LLM/UTH_IPSS_Pediatric Stroke/Instructor/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA83A4D4-BEBB-6046-BD34-89387FFB1316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE84B3A8-1CE0-704B-A585-79D2CDE60E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36560" yWindow="-1240" windowWidth="38400" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSOM_total (100% correct)" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="417">
   <si>
     <t>filename</t>
   </si>
@@ -1282,13 +1282,29 @@
   </si>
   <si>
     <t>they are correct from the beginning</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CTA, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>MRI</t>
+    </r>
+  </si>
+  <si>
+    <t>Human Review - Dulin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,6 +1335,18 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1440,7 +1468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1510,6 +1538,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5570,1101 +5603,1178 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="31.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" style="5" customWidth="1"/>
+    <col min="8" max="9" width="15.33203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="G1" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>40</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>38</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>140</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2"/>
+      <c r="K5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>0</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="K6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="10"/>
+      <c r="H7" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="2"/>
+      <c r="J7" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2"/>
+      <c r="K8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="7"/>
+      <c r="H9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="2"/>
+      <c r="K9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>140</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2"/>
+      <c r="K10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="2"/>
+      <c r="K11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="2"/>
+      <c r="K12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="I13" s="2"/>
+      <c r="J13" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2"/>
+      <c r="K14" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>3</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>140</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="2"/>
+      <c r="K15" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>140</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="10"/>
+      <c r="H16" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="2"/>
+      <c r="J16" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>39</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="I17" s="2"/>
+      <c r="J17" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>50</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2"/>
+      <c r="K18" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>140</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="2"/>
+      <c r="K19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>49</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="10" t="s">
+      <c r="D20" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="I20" s="2"/>
+      <c r="J20" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="2"/>
+      <c r="K21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>45</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>140</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="2"/>
+      <c r="K22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>32</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="2"/>
+      <c r="K23" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>28</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="G24" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K24" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>46</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>140</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="10"/>
+      <c r="H25" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="I25" s="2"/>
+      <c r="J25" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>140</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2"/>
+      <c r="K26" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>16</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>140</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="2"/>
+      <c r="K27" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="2"/>
+      <c r="K28" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="I29" s="2"/>
+      <c r="J29" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="2"/>
+      <c r="K30" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>15</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="2"/>
+      <c r="K31" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>5</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="G32" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="I32" s="2"/>
+      <c r="J32" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>2</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="2"/>
+      <c r="K33" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="K34" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>140</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="K35" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>140</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="10"/>
+      <c r="H36" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="I36" s="2"/>
+      <c r="J36" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>27</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>140</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="2"/>
+      <c r="K37" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>18</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>140</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="2"/>
+      <c r="K38" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>23</v>
       </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="K39" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>1</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>142</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="2"/>
+      <c r="K40" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>19</v>
       </c>
       <c r="B41" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>140</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="2"/>
+      <c r="K41" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>25</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>140</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="2"/>
+      <c r="K42" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>7</v>
       </c>
       <c r="B43" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>140</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="2"/>
+      <c r="K43" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>9</v>
       </c>
       <c r="B44" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>140</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="2"/>
+      <c r="K44" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>21</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>140</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="2"/>
+      <c r="K45" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>17</v>
       </c>
       <c r="B46" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>140</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="2"/>
+      <c r="K46" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="G47" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="I47" s="2"/>
+      <c r="J47" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="I47" t="s">
+      <c r="K47" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="G48" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="2"/>
+      <c r="K48" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>140</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="2"/>
+      <c r="K49" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>30</v>
       </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>140</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="2"/>
+      <c r="K50" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>26</v>
       </c>
       <c r="B51" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>140</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="2"/>
+      <c r="K51" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>31</v>
       </c>
       <c r="B52" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="H52" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="2"/>
+      <c r="K52" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F55" s="5" t="s">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G55" s="5" t="s">
         <v>378</v>
       </c>
     </row>

--- a/output/results_0221_KB_review.xlsx
+++ b/output/results_0221_KB_review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dulin/Dropbox/UTHealth/SAFElab/LLM/UTH_IPSS_Pediatric Stroke/Instructor/output/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dulin/Dropbox/UTHealth/SAFElab/LLM/UTH_IPSS_Pediatric Stroke/IPSS-GPT/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE84B3A8-1CE0-704B-A585-79D2CDE60E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3606F145-785C-4440-A926-99D8294F4813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36560" yWindow="-1240" windowWidth="38400" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-1980" windowWidth="38400" windowHeight="19860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSOM_total (100% correct)" sheetId="1" r:id="rId1"/>
@@ -1468,7 +1468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1539,7 +1539,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4538,7 +4537,7 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -5750,17 +5749,16 @@
       <c r="A6" s="3">
         <v>0</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="D6" t="s">
         <v>140</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="29" t="s">
         <v>386</v>
       </c>
       <c r="K6" t="s">
@@ -6410,7 +6408,7 @@
       <c r="H34" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="28" t="s">
         <v>186</v>
       </c>
       <c r="K34" t="s">
@@ -6430,7 +6428,7 @@
       <c r="H35" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I35" s="29" t="s">
+      <c r="I35" s="28" t="s">
         <v>156</v>
       </c>
       <c r="K35" t="s">
@@ -6511,7 +6509,7 @@
       <c r="H39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I39" s="29" t="s">
+      <c r="I39" s="28" t="s">
         <v>156</v>
       </c>
       <c r="K39" t="s">

--- a/output/results_0221_KB_review.xlsx
+++ b/output/results_0221_KB_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dulin/Dropbox/UTHealth/SAFElab/LLM/UTH_IPSS_Pediatric Stroke/IPSS-GPT/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3606F145-785C-4440-A926-99D8294F4813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DB5858-56C3-7E47-B534-68FB8531C517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1980" windowWidth="38400" windowHeight="19860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34920" yWindow="-1400" windowWidth="18540" windowHeight="19860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSOM_total (100% correct)" sheetId="1" r:id="rId1"/>
